--- a/data/노임단가.xlsx
+++ b/data/노임단가.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>샘플 일위대가 값. 최신 노임으로 고치세요.</t>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1075</t>
         </is>
       </c>
     </row>
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>172698</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>노임단가를 입력하세요.</t>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1002</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>샘플 일위대가 값. 최신 노임으로 고치세요.</t>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1078</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>저압케이블전공과 같게 시작. 필요하면 수정.</t>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1078</t>
         </is>
       </c>
     </row>
@@ -500,11 +500,1631 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>376049</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>노임단가를 입력하세요.</t>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>특고압케이블전공</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>444519</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>플랜트케이블전공</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>263300</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>송전전공</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>645607</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>송전활선전공</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>685744</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>배전전공</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>420978</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1081</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>배전활선전공</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>562067</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>플랜트전공</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>269471</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1083</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>계장공</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>321645</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1084</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>철도신호공</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>318257</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>통신내선공</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>286219</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1086</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>통신설비공</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>316875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1087</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>통신외선공</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>410182</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1088</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>통신케이블공</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>438070</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1089</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>무선안테나공</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>360084</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1090</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>전기공사기사</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>339070</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5004</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>전기공사산업기사</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>298573</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5005</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>변전전공</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>485593</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5006</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>전철전공</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>429783</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5016</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>작업반장</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>218316</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>특별인부</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>228717</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>조력공</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>181496</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>제도사</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>242423</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>비계공</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>284440</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>형틀목공</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>275379</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>철근공</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>268932</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>철공</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>243870</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>철판공</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>220901</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>철골공</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>255172</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>용접공</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>286330</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>콘크리트공</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>276285</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>보링공</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>233503</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1014</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>착암공</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>223246</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>화약취급공</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>270444</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>할석공</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>246224</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1017</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>포설공</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>221306</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>포장공</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>274873</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>잠수부</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>391240</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>조적공</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>273229</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1021</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>견출공</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>254875</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>건축목공</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>282990</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>창호공</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>248547</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>유리공</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>258602</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>방수공</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>233163</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>미장공</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>279102</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>타일공</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>294379</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>도장공</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>268225</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>내장공</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>258904</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>도배공</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>229833</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>연마공</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>208207</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>석공</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>270694</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>줄눈공</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>212390</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>판넬조립공</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>246986</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>벌목부</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>257444</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>조경공</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>235843</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>배관공</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>249073</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>배관공(수도)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>260673</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>보일러공</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>240647</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1041</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>위생공</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>221435</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1042</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>덕트공</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>208140</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>보온공</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>222151</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>인력운반공</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>183687</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>궤도공</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>220821</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>건설기계운전사</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>283323</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>화물차운전사</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>240042</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>기계설비공</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>242647</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>플랜트배관공</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>327442</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>플랜트제관공</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>268949</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>플랜트용접공</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>289745</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>플랜트특수용접공</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>334739</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1059</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>플랜트기계설치공</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>234041</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>플랜트특별인부</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>215601</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1061</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>플랜트계장공</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>204167</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1063</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>플랜트보온공</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>252567</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1065</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>제철축로공</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>365714</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>비파괴시험공</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>220565</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>특급품질관리원</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>200971</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>고급품질관리원</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>199200</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>중급품질관리원</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>179012</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1070</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>초급품질관리원</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>150049</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>지적기사</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>283066</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>지적산업기사</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>251236</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>지적기능사</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>175118</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>석면해체공</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>203461</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1091</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>광케이블설치사</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>471931</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>H/W시험사</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>398279</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>S/W시험사</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>446560</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>도편수</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>533333</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>한식목공</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>353383</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>한식석공</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>403594</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>한식와공</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>374046</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>화공</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>300798</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>한식미장공편수</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>395789</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>원자력플랜트전공</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>238957</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>원자력용접공</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>220497</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4002</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>원자력기계설치공</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>244723</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>원자력품질관리사</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>287101</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4004</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>통신관련기사</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>324979</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>통신관련산업기사</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>304662</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5002</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>통신관련기능사</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5003</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>코킹공</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>212439</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5007</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>특급품질관리기술인</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>272695</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5008</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>고급품질관리기술인</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>221341</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5009</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>중급품질관리기술인</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>193319</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5010</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>초급품질관리기술인</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>167631</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5011</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>플로어링마루시공공</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>257926</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5012</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>교통정리원</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>176930</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5013</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>철거공</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>261108</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5014</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>흙막이공</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>272418</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5015</t>
         </is>
       </c>
     </row>

--- a/data/노임단가.xlsx
+++ b/data/노임단가.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="굴림"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="굴림"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7DEE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +61,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,1715 +456,1720 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="25"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>직종</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>노임단가</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>내선전공</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>276108</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1075</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>보통인부</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>172698</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1002</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>저압케이블전공</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>306274</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1078</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>케이블전공</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>306274</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1078</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>고압케이블전공</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>376049</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1077</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>특고압케이블전공</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>444519</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1076</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>플랜트케이블전공</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>263300</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1062</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>송전전공</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>645607</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1079</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>송전활선전공</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>685744</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1080</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>배전전공</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>420978</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1081</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>배전활선전공</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>562067</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1082</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>플랜트전공</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>269471</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1083</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>계장공</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>321645</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1084</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>철도신호공</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>318257</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1085</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>통신내선공</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>286219</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1086</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>통신설비공</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>316875</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1087</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>통신외선공</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>410182</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1088</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>통신케이블공</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>438070</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1089</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>무선안테나공</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>360084</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1090</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>전기공사기사</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>339070</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5004</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>전기공사산업기사</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="3" t="n">
         <v>298573</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5005</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>변전전공</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>485593</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5006</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>전철전공</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>429783</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5016</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>작업반장</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="3" t="n">
         <v>218316</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1001</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>특별인부</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>228717</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1003</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>조력공</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>181496</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1004</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>제도사</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>242423</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1005</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>비계공</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="3" t="n">
         <v>284440</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1006</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>형틀목공</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>275379</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1007</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>철근공</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="3" t="n">
         <v>268932</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1008</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>철공</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="3" t="n">
         <v>243870</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1009</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>철판공</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="3" t="n">
         <v>220901</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1010</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>철골공</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="3" t="n">
         <v>255172</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1011</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>용접공</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="3" t="n">
         <v>286330</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1012</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>콘크리트공</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="3" t="n">
         <v>276285</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1013</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>보링공</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="3" t="n">
         <v>233503</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1014</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>착암공</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="3" t="n">
         <v>223246</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1015</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" ht="25" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>화약취급공</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="3" t="n">
         <v>270444</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1016</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>할석공</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="3" t="n">
         <v>246224</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1017</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="41" ht="25" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>포설공</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="3" t="n">
         <v>221306</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1018</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>포장공</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="3" t="n">
         <v>274873</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1019</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>잠수부</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="3" t="n">
         <v>391240</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1020</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="44" ht="25" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>조적공</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="3" t="n">
         <v>273229</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1021</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="45" ht="25" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>견출공</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="3" t="n">
         <v>254875</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1022</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="46" ht="25" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>건축목공</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="3" t="n">
         <v>282990</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1023</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="47" ht="25" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>창호공</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="3" t="n">
         <v>248547</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1024</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="48" ht="25" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>유리공</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="3" t="n">
         <v>258602</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1025</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="49" ht="25" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>방수공</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="3" t="n">
         <v>233163</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1026</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="50" ht="25" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>미장공</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="3" t="n">
         <v>279102</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1027</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>타일공</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="3" t="n">
         <v>294379</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1028</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>도장공</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="3" t="n">
         <v>268225</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1029</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="53" ht="25" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>내장공</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="3" t="n">
         <v>258904</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1030</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="54" ht="25" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>도배공</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="3" t="n">
         <v>229833</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1031</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>연마공</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="3" t="n">
         <v>208207</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1032</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>석공</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="3" t="n">
         <v>270694</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1033</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="57" ht="25" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>줄눈공</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="3" t="n">
         <v>212390</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1034</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>판넬조립공</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="3" t="n">
         <v>246986</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1035</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="59" ht="25" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>벌목부</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="3" t="n">
         <v>257444</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1037</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>조경공</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="3" t="n">
         <v>235843</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1038</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>배관공</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="3" t="n">
         <v>249073</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1039</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="62" ht="25" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>배관공(수도)</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="3" t="n">
         <v>260673</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1040</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="63" ht="25" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>보일러공</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="3" t="n">
         <v>240647</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1041</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="64" ht="25" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>위생공</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="3" t="n">
         <v>221435</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1042</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="65" ht="25" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>덕트공</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="3" t="n">
         <v>208140</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1043</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="66" ht="25" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>보온공</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="3" t="n">
         <v>222151</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1044</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="67" ht="25" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>인력운반공</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="3" t="n">
         <v>183687</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1045</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="68" ht="25" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>궤도공</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="3" t="n">
         <v>220821</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1046</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="69" ht="25" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>건설기계운전사</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="3" t="n">
         <v>283323</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1048</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="70" ht="25" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>화물차운전사</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="3" t="n">
         <v>240042</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1049</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="71" ht="25" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>기계설비공</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="3" t="n">
         <v>242647</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1051</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="72" ht="25" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>플랜트배관공</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="3" t="n">
         <v>327442</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1056</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="73" ht="25" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>플랜트제관공</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="3" t="n">
         <v>268949</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1057</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="74" ht="25" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>플랜트용접공</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="3" t="n">
         <v>289745</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1058</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="75" ht="25" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>플랜트특수용접공</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="3" t="n">
         <v>334739</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1059</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="76" ht="25" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>플랜트기계설치공</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="3" t="n">
         <v>234041</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1060</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="77" ht="25" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>플랜트특별인부</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="3" t="n">
         <v>215601</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1061</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="78" ht="25" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>플랜트계장공</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="3" t="n">
         <v>204167</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1063</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="79" ht="25" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>플랜트보온공</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="3" t="n">
         <v>252567</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1065</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="80" ht="25" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>제철축로공</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="3" t="n">
         <v>365714</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1066</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="81" ht="25" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>비파괴시험공</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="3" t="n">
         <v>220565</v>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1067</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="82" ht="25" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>특급품질관리원</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="3" t="n">
         <v>200971</v>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1068</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="83" ht="25" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>고급품질관리원</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="3" t="n">
         <v>199200</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1069</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="84" ht="25" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>중급품질관리원</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="3" t="n">
         <v>179012</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1070</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="85" ht="25" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>초급품질관리원</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="3" t="n">
         <v>150049</v>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1071</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="86" ht="25" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>지적기사</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="3" t="n">
         <v>283066</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1072</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="87" ht="25" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>지적산업기사</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="3" t="n">
         <v>251236</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1073</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="88" ht="25" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>지적기능사</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="3" t="n">
         <v>175118</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1074</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="89" ht="25" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>석면해체공</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="3" t="n">
         <v>203461</v>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 1091</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="90" ht="25" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>광케이블설치사</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="3" t="n">
         <v>471931</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2001</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="91" ht="25" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>H/W시험사</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="3" t="n">
         <v>398279</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2002</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="92" ht="25" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>S/W시험사</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="3" t="n">
         <v>446560</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 2003</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="93" ht="25" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>도편수</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="3" t="n">
         <v>533333</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3001</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="94" ht="25" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>한식목공</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="3" t="n">
         <v>353383</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3003</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="95" ht="25" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>한식석공</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="3" t="n">
         <v>403594</v>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3005</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="96" ht="25" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>한식와공</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="3" t="n">
         <v>374046</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3007</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="97" ht="25" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>화공</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="3" t="n">
         <v>300798</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3012</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="98" ht="25" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>한식미장공편수</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="3" t="n">
         <v>395789</v>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 3014</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="99" ht="25" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>원자력플랜트전공</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="3" t="n">
         <v>238957</v>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4001</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="100" ht="25" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>원자력용접공</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="3" t="n">
         <v>220497</v>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4002</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="101" ht="25" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>원자력기계설치공</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="3" t="n">
         <v>244723</v>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4003</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="102" ht="25" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>원자력품질관리사</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="3" t="n">
         <v>287101</v>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 4004</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="103" ht="25" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>통신관련기사</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="3" t="n">
         <v>324979</v>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5001</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="104" ht="25" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>통신관련산업기사</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="3" t="n">
         <v>304662</v>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5002</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="105" ht="25" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>통신관련기능사</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="3" t="n">
         <v>250000</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5003</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="106" ht="25" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>코킹공</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="3" t="n">
         <v>212439</v>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5007</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="107" ht="25" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>특급품질관리기술인</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="3" t="n">
         <v>272695</v>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5008</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="108" ht="25" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>고급품질관리기술인</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="3" t="n">
         <v>221341</v>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5009</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="109" ht="25" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>중급품질관리기술인</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="3" t="n">
         <v>193319</v>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5010</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="110" ht="25" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>초급품질관리기술인</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="3" t="n">
         <v>167631</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5011</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="111" ht="25" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>플로어링마루시공공</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="3" t="n">
         <v>257926</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5012</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="112" ht="25" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>교통정리원</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="3" t="n">
         <v>176930</v>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5013</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="113" ht="25" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>철거공</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="3" t="n">
         <v>261108</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5014</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="114" ht="25" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>흙막이공</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="3" t="n">
         <v>272418</v>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>2026년 하반기 시중노임 (2026.9.1 적용) · 5015</t>
         </is>
